--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487538_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487538_PROCESSED_CHRONO.xlsx
@@ -565,10 +565,10 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.307</v>
+        <v>8.4094</v>
       </c>
       <c r="E2" t="n">
-        <v>7.4095</v>
+        <v>7.5118</v>
       </c>
       <c r="F2" t="n">
         <v>0.8975</v>
@@ -610,10 +610,10 @@
         <v>3.1336</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6228</v>
+        <v>0.7252</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6516</v>
+        <v>0.754</v>
       </c>
       <c r="U2" t="n">
         <v>-0.0288</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>K. VAN WIJK</t>
+          <t>H. REY PEREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,40 +643,40 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7658</v>
+        <v>4.4973</v>
       </c>
       <c r="E3" t="n">
-        <v>2.5781</v>
+        <v>6.8383</v>
       </c>
       <c r="F3" t="n">
-        <v>2.1877</v>
+        <v>-2.3409</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5669</v>
+        <v>2.6226</v>
       </c>
       <c r="H3" t="n">
-        <v>1.0412</v>
+        <v>2.1532</v>
       </c>
       <c r="I3" t="n">
-        <v>0.5258</v>
+        <v>0.4694</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2139</v>
+        <v>6.387</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9714</v>
+        <v>2.6948</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2425</v>
+        <v>3.6922</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3531</v>
+        <v>-3.7645</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0698</v>
+        <v>-0.5416</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2833</v>
+        <v>-3.2228</v>
       </c>
       <c r="P3" t="n">
         <v>0.7834</v>
@@ -688,22 +688,22 @@
         <v>1.7626</v>
       </c>
       <c r="S3" t="n">
-        <v>1.1989</v>
+        <v>1.0338</v>
       </c>
       <c r="T3" t="n">
-        <v>1.1269</v>
+        <v>0.8222</v>
       </c>
       <c r="U3" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.2116</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2166</v>
+        <v>0.0576</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2166</v>
+        <v>0.6083</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.4621</v>
+        <v>4.4353</v>
       </c>
       <c r="E4" t="n">
         <v>2.1603</v>
       </c>
       <c r="F4" t="n">
-        <v>2.3017</v>
+        <v>2.275</v>
       </c>
       <c r="G4" t="n">
         <v>4.6541</v>
@@ -766,13 +766,13 @@
         <v>1.5668</v>
       </c>
       <c r="S4" t="n">
-        <v>0.475</v>
+        <v>0.4483</v>
       </c>
       <c r="T4" t="n">
         <v>0.2247</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2504</v>
+        <v>0.2236</v>
       </c>
       <c r="V4" t="n">
         <v>-0.2754</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. FILGUEIRA BUCETA</t>
+          <t>K. VAN WIJK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.2517</v>
+        <v>4.3624</v>
       </c>
       <c r="E5" t="n">
-        <v>3.7978</v>
+        <v>2.2282</v>
       </c>
       <c r="F5" t="n">
-        <v>0.4539</v>
+        <v>2.1342</v>
       </c>
       <c r="G5" t="n">
-        <v>1.7871</v>
+        <v>1.5669</v>
       </c>
       <c r="H5" t="n">
-        <v>1.0745</v>
+        <v>1.0412</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7126</v>
+        <v>0.5258</v>
       </c>
       <c r="J5" t="n">
-        <v>2.6517</v>
+        <v>1.2139</v>
       </c>
       <c r="K5" t="n">
-        <v>1.2776</v>
+        <v>0.9714</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3741</v>
+        <v>0.2425</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.8646</v>
+        <v>0.3531</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2031</v>
+        <v>0.0698</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6615</v>
+        <v>0.2833</v>
       </c>
       <c r="P5" t="n">
-        <v>0.3917</v>
+        <v>0.7834</v>
       </c>
       <c r="Q5" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3709</v>
+        <v>1.7626</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5809</v>
+        <v>0.7955</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9663</v>
+        <v>0.7769</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3854</v>
+        <v>0.0185</v>
       </c>
       <c r="V5" t="n">
-        <v>1.492</v>
+        <v>1.2166</v>
       </c>
       <c r="W5" t="n">
-        <v>1.159</v>
+        <v>1.2166</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3329</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. REY PEREZ</t>
+          <t>A. FILGUEIRA BUCETA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>3.8612</v>
+        <v>3.9806</v>
       </c>
       <c r="E6" t="n">
-        <v>6.1219</v>
+        <v>3.2861</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.2607</v>
+        <v>0.6945</v>
       </c>
       <c r="G6" t="n">
-        <v>2.6226</v>
+        <v>1.7871</v>
       </c>
       <c r="H6" t="n">
-        <v>2.1532</v>
+        <v>1.0745</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4694</v>
+        <v>0.7126</v>
       </c>
       <c r="J6" t="n">
-        <v>6.387</v>
+        <v>2.6517</v>
       </c>
       <c r="K6" t="n">
-        <v>2.6948</v>
+        <v>1.2776</v>
       </c>
       <c r="L6" t="n">
-        <v>3.6922</v>
+        <v>1.3741</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.7645</v>
+        <v>-0.8646</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5416</v>
+        <v>-0.2031</v>
       </c>
       <c r="O6" t="n">
-        <v>-3.2228</v>
+        <v>-0.6615</v>
       </c>
       <c r="P6" t="n">
-        <v>0.7834</v>
+        <v>0.3917</v>
       </c>
       <c r="Q6" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7626</v>
+        <v>1.3709</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3976</v>
+        <v>0.3098</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1059</v>
+        <v>0.4546</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2918</v>
+        <v>-0.1448</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0576</v>
+        <v>1.492</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6083</v>
+        <v>1.159</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5507</v>
+        <v>0.3329</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.6544</v>
+        <v>3.5756</v>
       </c>
       <c r="E7" t="n">
-        <v>1.5737</v>
+        <v>1.7355</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0807</v>
+        <v>1.8401</v>
       </c>
       <c r="G7" t="n">
         <v>2.0835</v>
@@ -1000,13 +1000,13 @@
         <v>1.5668</v>
       </c>
       <c r="S7" t="n">
-        <v>1.2588</v>
+        <v>1.1799</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4205</v>
+        <v>0.5823</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8383</v>
+        <v>0.5977</v>
       </c>
       <c r="V7" t="n">
         <v>-0.2754</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>2.1313</v>
+        <v>2.3732</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6144</v>
+        <v>1.7761</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5169</v>
+        <v>0.5971</v>
       </c>
       <c r="G8" t="n">
         <v>0.9615</v>
@@ -1078,13 +1078,13 @@
         <v>1.1751</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3382</v>
+        <v>-0.0963</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1429</v>
+        <v>0.0188</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1953</v>
+        <v>-0.1151</v>
       </c>
       <c r="V8" t="n">
         <v>0.3329</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0331</v>
+        <v>0.053</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7805</v>
+        <v>-1.7211</v>
       </c>
       <c r="F9" t="n">
-        <v>1.7474</v>
+        <v>1.7741</v>
       </c>
       <c r="G9" t="n">
         <v>-2.8705</v>
@@ -1156,13 +1156,13 @@
         <v>3.1336</v>
       </c>
       <c r="S9" t="n">
-        <v>0.3501</v>
+        <v>0.4362</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4734</v>
+        <v>0.5328000000000001</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1233</v>
+        <v>-0.09660000000000001</v>
       </c>
       <c r="V9" t="n">
         <v>0.3329</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0371</v>
+        <v>-1.6732</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.1385</v>
+        <v>-0.8549</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.8985</v>
+        <v>-0.8184</v>
       </c>
       <c r="G10" t="n">
         <v>-1.5528</v>
@@ -1234,13 +1234,13 @@
         <v>0.1958</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2991</v>
+        <v>0.663</v>
       </c>
       <c r="T10" t="n">
-        <v>1.2457</v>
+        <v>0.5293</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0535</v>
+        <v>0.1337</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>D. HOGAN</t>
+          <t>A. BOUZAN CUMPLIDO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.465</v>
+        <v>-3.3091</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.063</v>
+        <v>-1.9146</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.402</v>
+        <v>-1.3944</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.3673</v>
+        <v>-4.1645</v>
       </c>
       <c r="H11" t="n">
-        <v>0.9864000000000001</v>
+        <v>-2.123</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.3537</v>
+        <v>-2.0415</v>
       </c>
       <c r="J11" t="n">
-        <v>1.3066</v>
+        <v>-0.7479</v>
       </c>
       <c r="K11" t="n">
-        <v>0.9833</v>
+        <v>-1.3782</v>
       </c>
       <c r="L11" t="n">
-        <v>0.3233</v>
+        <v>0.6303</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.6739</v>
+        <v>-3.4166</v>
       </c>
       <c r="N11" t="n">
-        <v>0.0031</v>
+        <v>-0.7447</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.677</v>
+        <v>-2.6718</v>
       </c>
       <c r="P11" t="n">
-        <v>-2.7419</v>
+        <v>0.7834</v>
       </c>
       <c r="Q11" t="n">
-        <v>-3.917</v>
+        <v>-1.9585</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1751</v>
+        <v>2.7419</v>
       </c>
       <c r="S11" t="n">
-        <v>2.1362</v>
+        <v>0.4049</v>
       </c>
       <c r="T11" t="n">
-        <v>1.5474</v>
+        <v>0.5164</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5888</v>
+        <v>-0.1114</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.492</v>
+        <v>-0.3329</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.492</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. BOUZAN CUMPLIDO</t>
+          <t>D. HOGAN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.7523</v>
+        <v>-4.2616</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.3044</v>
+        <v>-1.7794</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4479</v>
+        <v>-2.4822</v>
       </c>
       <c r="G12" t="n">
-        <v>-4.1645</v>
+        <v>-1.3673</v>
       </c>
       <c r="H12" t="n">
-        <v>-2.123</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.0415</v>
+        <v>-2.3537</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.7479</v>
+        <v>1.3066</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.3782</v>
+        <v>0.9833</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6303</v>
+        <v>0.3233</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.4166</v>
+        <v>-2.6739</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7447</v>
+        <v>0.0031</v>
       </c>
       <c r="O12" t="n">
-        <v>-2.6718</v>
+        <v>-2.677</v>
       </c>
       <c r="P12" t="n">
-        <v>0.7834</v>
+        <v>-2.7419</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.9585</v>
+        <v>-3.917</v>
       </c>
       <c r="R12" t="n">
-        <v>2.7419</v>
+        <v>1.1751</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.0383</v>
+        <v>1.3396</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8734</v>
+        <v>0.831</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.1649</v>
+        <v>0.5086000000000001</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3329</v>
+        <v>-1.492</v>
       </c>
       <c r="W12" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.6083</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>22.146</v>
+        <v>22.44289999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>18.9693</v>
+        <v>19.2663</v>
       </c>
       <c r="F13" t="n">
-        <v>3.1767</v>
+        <v>3.1766</v>
       </c>
       <c r="G13" t="n">
         <v>8.775699999999999</v>
@@ -1438,7 +1438,7 @@
         <v>4.7601</v>
       </c>
       <c r="I13" t="n">
-        <v>4.0156</v>
+        <v>4.015599999999998</v>
       </c>
       <c r="J13" t="n">
         <v>22.0777</v>
@@ -1468,16 +1468,16 @@
         <v>19.5848</v>
       </c>
       <c r="S13" t="n">
-        <v>6.9429</v>
+        <v>7.2399</v>
       </c>
       <c r="T13" t="n">
-        <v>5.7461</v>
+        <v>6.042999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>1.1971</v>
+        <v>1.197</v>
       </c>
       <c r="V13" t="n">
-        <v>3.489500000000001</v>
+        <v>3.489499999999999</v>
       </c>
       <c r="W13" t="n">
         <v>7.792800000000001</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4805</v>
+        <v>0.7534</v>
       </c>
       <c r="E14" t="n">
         <v>3.7503</v>
       </c>
       <c r="F14" t="n">
-        <v>-3.2698</v>
+        <v>-2.9969</v>
       </c>
       <c r="G14" t="n">
         <v>-1.5151</v>
@@ -1546,13 +1546,13 @@
         <v>2.9377</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6086</v>
+        <v>-1.3357</v>
       </c>
       <c r="T14" t="n">
         <v>-0.4288</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.1798</v>
+        <v>-0.9069</v>
       </c>
       <c r="V14" t="n">
         <v>1.6457</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.9077</v>
+        <v>-0.7639</v>
       </c>
       <c r="E15" t="n">
-        <v>2.9365</v>
+        <v>2.8342</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.8442</v>
+        <v>-3.598</v>
       </c>
       <c r="G15" t="n">
         <v>1.2238</v>
@@ -1624,13 +1624,13 @@
         <v>1.9585</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.973</v>
+        <v>-0.8290999999999999</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0047</v>
+        <v>-0.09760000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9777</v>
+        <v>-0.7315</v>
       </c>
       <c r="V15" t="n">
         <v>-0.1792</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.7983</v>
+        <v>-1.3355</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.228</v>
+        <v>-0.8186</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5703</v>
+        <v>-0.5169</v>
       </c>
       <c r="G16" t="n">
         <v>-1.2464</v>
@@ -1702,13 +1702,13 @@
         <v>0.9792</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-0.0891</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4752</v>
+        <v>-0.0659</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0767</v>
+        <v>-0.0232</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. SAN MILLAN GONZALEZ-QUEVEDO</t>
+          <t>D. BLANCO RAMOS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.1955</v>
+        <v>-2.2459</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1422</v>
+        <v>-1.7349</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.3377</v>
+        <v>-0.511</v>
       </c>
       <c r="G17" t="n">
-        <v>-1.4792</v>
+        <v>-0.6225000000000001</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2623</v>
+        <v>-0.3396</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.2169</v>
+        <v>-0.2829</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3854</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>0.1429</v>
+        <v>0</v>
       </c>
       <c r="L17" t="n">
-        <v>0.2425</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.8646</v>
+        <v>-0.0615</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4052</v>
+        <v>-0.3396</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.4594</v>
+        <v>0.2781</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7834</v>
+        <v>-0.7834</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R17" t="n">
-        <v>1.7626</v>
+        <v>0.1958</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1075</v>
+        <v>-0.2894</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.09</v>
+        <v>-0.1947</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1974</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.6071</v>
+        <v>-0.5507</v>
       </c>
       <c r="W17" t="n">
-        <v>0.8260999999999999</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-2.4332</v>
+        <v>-0.5507</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R. PEREZ MARTIN</t>
+          <t>M. SAN MILLAN GONZALEZ-QUEVEDO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.2061</v>
+        <v>-2.4554</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5381</v>
+        <v>0.0399</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.6679</v>
+        <v>-2.4953</v>
       </c>
       <c r="G18" t="n">
-        <v>0.6877</v>
+        <v>-1.4792</v>
       </c>
       <c r="H18" t="n">
-        <v>0.0762</v>
+        <v>-0.2623</v>
       </c>
       <c r="I18" t="n">
-        <v>0.6114000000000001</v>
+        <v>-1.2169</v>
       </c>
       <c r="J18" t="n">
-        <v>3.0251</v>
+        <v>0.3854</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6365</v>
+        <v>0.1429</v>
       </c>
       <c r="L18" t="n">
-        <v>1.3886</v>
+        <v>0.2425</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.3375</v>
+        <v>-1.8646</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5603</v>
+        <v>-0.4052</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.7772</v>
+        <v>-1.4594</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.1543</v>
+        <v>0.7834</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.8962</v>
+        <v>-0.9792</v>
       </c>
       <c r="R18" t="n">
-        <v>2.7419</v>
+        <v>1.7626</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2848</v>
+        <v>-0.1525</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4493</v>
+        <v>-0.1923</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7341</v>
+        <v>0.0399</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.4546</v>
+        <v>-1.6071</v>
       </c>
       <c r="W18" t="n">
-        <v>0.8837</v>
+        <v>0.8260999999999999</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.3383</v>
+        <v>-2.4332</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. BLANCO RAMOS</t>
+          <t>R. PEREZ MARTIN</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5916</v>
+        <v>-2.4835</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8372</v>
+        <v>-0.8451</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7544</v>
+        <v>-1.6384</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.6225000000000001</v>
+        <v>0.6877</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.3396</v>
+        <v>0.0762</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2829</v>
+        <v>0.6114000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5610000000000001</v>
+        <v>3.0251</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>1.6365</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.5610000000000001</v>
+        <v>1.3886</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0615</v>
+        <v>-2.3375</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3396</v>
+        <v>-1.5603</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2781</v>
+        <v>-0.7772</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.7834</v>
+        <v>-2.1543</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9792</v>
+        <v>-4.8962</v>
       </c>
       <c r="R19" t="n">
-        <v>0.1958</v>
+        <v>2.7419</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6351</v>
+        <v>-0.5623</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.297</v>
+        <v>0.1423</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.3381</v>
+        <v>-0.7046</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.5507</v>
+        <v>-0.4546</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.8837</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5507</v>
+        <v>-1.3383</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.3269</v>
+        <v>-2.925</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.3574</v>
+        <v>-1.2551</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9695</v>
+        <v>-1.6699</v>
       </c>
       <c r="G20" t="n">
         <v>-1.2117</v>
@@ -2014,13 +2014,13 @@
         <v>2.7419</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.7978</v>
+        <v>-1.3958</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.607</v>
+        <v>-0.5046</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.1908</v>
+        <v>-0.8912</v>
       </c>
       <c r="V20" t="n">
         <v>-0.1217</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. NONGO N'SALA</t>
+          <t>Y. IGLESIAS MENDEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.4772</v>
+        <v>-4.1054</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.3569</v>
+        <v>-3.074</v>
       </c>
       <c r="F21" t="n">
-        <v>-3.1203</v>
+        <v>-1.0314</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.1741</v>
+        <v>-2.4382</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.3205</v>
+        <v>0.5780999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.8535</v>
+        <v>-3.0163</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.5606</v>
+        <v>0.1649</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6414</v>
+        <v>0.9135</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0808</v>
+        <v>-0.7486</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6135</v>
+        <v>-2.6031</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6791</v>
+        <v>-0.3354</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9344</v>
+        <v>-2.2677</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.1751</v>
+        <v>-0.3917</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9585</v>
+        <v>-2.9377</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7834</v>
+        <v>2.546</v>
       </c>
       <c r="S21" t="n">
-        <v>0.8185</v>
+        <v>-1.0001</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1622</v>
+        <v>-0.3011</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3436</v>
+        <v>-0.699</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.9466</v>
+        <v>-0.2754</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.9466</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Y. IGLESIAS MENDEZ</t>
+          <t>A. NONGO N'SALA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.1232</v>
+        <v>-5.2203</v>
       </c>
       <c r="E22" t="n">
-        <v>-3.688</v>
+        <v>-2.0733</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4352</v>
+        <v>-3.147</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.4382</v>
+        <v>-2.1741</v>
       </c>
       <c r="H22" t="n">
-        <v>0.5780999999999999</v>
+        <v>-1.3205</v>
       </c>
       <c r="I22" t="n">
-        <v>-3.0163</v>
+        <v>-0.8535</v>
       </c>
       <c r="J22" t="n">
-        <v>0.1649</v>
+        <v>-0.5606</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9135</v>
+        <v>-0.6414</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.7486</v>
+        <v>0.0808</v>
       </c>
       <c r="M22" t="n">
-        <v>-2.6031</v>
+        <v>-1.6135</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3354</v>
+        <v>-0.6791</v>
       </c>
       <c r="O22" t="n">
-        <v>-2.2677</v>
+        <v>-0.9344</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3917</v>
+        <v>-1.1751</v>
       </c>
       <c r="Q22" t="n">
-        <v>-2.9377</v>
+        <v>-1.9585</v>
       </c>
       <c r="R22" t="n">
-        <v>2.546</v>
+        <v>0.7834</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.0179</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.9151</v>
+        <v>0.4458</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1027</v>
+        <v>-0.3704</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.2754</v>
+        <v>-1.9466</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.2754</v>
+        <v>-1.9466</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-22.146</v>
+        <v>-20.7815</v>
       </c>
       <c r="E23" t="n">
         <v>-3.1766</v>
       </c>
       <c r="F23" t="n">
-        <v>-18.9693</v>
+        <v>-17.6048</v>
       </c>
       <c r="G23" t="n">
         <v>-8.775700000000001</v>
@@ -2239,7 +2239,7 @@
         <v>-14.6199</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.937600000000001</v>
+        <v>-2.9376</v>
       </c>
       <c r="Q23" t="n">
         <v>-19.5846</v>
@@ -2248,22 +2248,22 @@
         <v>16.647</v>
       </c>
       <c r="S23" t="n">
-        <v>-6.9431</v>
+        <v>-5.5786</v>
       </c>
       <c r="T23" t="n">
         <v>-1.1969</v>
       </c>
       <c r="U23" t="n">
-        <v>-5.7461</v>
+        <v>-4.3816</v>
       </c>
       <c r="V23" t="n">
         <v>-3.4896</v>
       </c>
       <c r="W23" t="n">
-        <v>4.303199999999999</v>
+        <v>4.3032</v>
       </c>
       <c r="X23" t="n">
-        <v>-7.7929</v>
+        <v>-7.792899999999999</v>
       </c>
     </row>
   </sheetData>
